--- a/questionnaire_templates/042_health_q_a_question_submission_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/042_health_q_a_question_submission_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'general',_'value':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'General', 'value': 'general'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'medical',_'value':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Medical', 'value': 'medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'social',_'value':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Social', 'value': 'social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'general',_'value':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'General', 'value': 'general'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'medical',_'value':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Medical', 'value': 'medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'social',_'value':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Social', 'value': 'social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'form_1',_'value':_'form_1'}</t>
+          <t>form_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Form 1', 'value': 'form_1'}</t>
+          <t>Form 1</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'form_2',_'value':_'form_2'}</t>
+          <t>form_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Form 2', 'value': 'form_2'}</t>
+          <t>Form 2</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
